--- a/GameData/DataTables/Board/LevelFixedElementTable.xlsx
+++ b/GameData/DataTables/Board/LevelFixedElementTable.xlsx
@@ -417,8 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="34" customWidth="1" min="18" max="18"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -513,6 +521,11 @@
           <t>RepairEnergyCost</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>InstanceData</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -595,6 +608,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -675,6 +693,11 @@
       <c r="Q4" t="inlineStr">
         <is>
           <t>单次维修能量消耗</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>实例关系 k=v；固定元素行ID</t>
         </is>
       </c>
     </row>
